--- a/elite-data/manifest-templates/EL_template_AssayProteomicsTemplate.xlsx
+++ b/elite-data/manifest-templates/EL_template_AssayProteomicsTemplate.xlsx
@@ -249,7 +249,7 @@
     <t>Label-free gene level quantitation</t>
   </si>
   <si>
-    <t>Not applicable</t>
+    <t>not applicable</t>
   </si>
   <si>
     <t>2-iodobenzoate</t>
@@ -279,7 +279,7 @@
     <t>Label-free protein group level quantitation</t>
   </si>
   <si>
-    <t>Not collected</t>
+    <t>not collected</t>
   </si>
   <si>
     <t>Asp-N</t>
@@ -318,7 +318,7 @@
     <t>IodoTMT</t>
   </si>
   <si>
-    <t>Unknown</t>
+    <t>unknown</t>
   </si>
   <si>
     <t>CNBr</t>
